--- a/8月25日水钢三棒加热炉调试记录.xlsx
+++ b/8月25日水钢三棒加热炉调试记录.xlsx
@@ -157,18 +157,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -516,18 +513,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
@@ -563,10 +560,10 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -586,10 +583,10 @@
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>0.62361111111111112</v>
       </c>
     </row>
@@ -599,46 +596,43 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="3"/>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
         <v>16</v>
       </c>
     </row>
